--- a/artfynd/A 25401-2026 artfynd.xlsx
+++ b/artfynd/A 25401-2026 artfynd.xlsx
@@ -675,53 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>134168910</v>
+        <v>134168911</v>
       </c>
       <c r="B2" t="n">
-        <v>99178</v>
+        <v>57972</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Vattentornet Bergsåker, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>615177</v>
+        <v>615173</v>
       </c>
       <c r="R2" t="n">
-        <v>6922983</v>
+        <v>6922963</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +755,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>11 st</t>
+          <t>Födosök</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,48 +787,53 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>134168911</v>
+        <v>134168910</v>
       </c>
       <c r="B3" t="n">
-        <v>57972</v>
+        <v>99178</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Vattentornet Bergsåker, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>615173</v>
+        <v>615177</v>
       </c>
       <c r="R3" t="n">
-        <v>6922963</v>
+        <v>6922983</v>
       </c>
       <c r="S3" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,12 +872,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Födosök</t>
+          <t>11 st</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 25401-2026 artfynd.xlsx
+++ b/artfynd/A 25401-2026 artfynd.xlsx
@@ -675,48 +675,53 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>134168911</v>
+        <v>134168910</v>
       </c>
       <c r="B2" t="n">
-        <v>57972</v>
+        <v>99180</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Vattentornet Bergsåker, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>615173</v>
+        <v>615177</v>
       </c>
       <c r="R2" t="n">
-        <v>6922963</v>
+        <v>6922983</v>
       </c>
       <c r="S2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,12 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Födosök</t>
+          <t>11 st</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,53 +792,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>134168910</v>
+        <v>134168911</v>
       </c>
       <c r="B3" t="n">
-        <v>99178</v>
+        <v>57972</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Vattentornet Bergsåker, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>615177</v>
+        <v>615173</v>
       </c>
       <c r="R3" t="n">
-        <v>6922983</v>
+        <v>6922963</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,12 +872,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>11 st</t>
+          <t>Födosök</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,7 +907,7 @@
         <v>134168909</v>
       </c>
       <c r="B4" t="n">
-        <v>99178</v>
+        <v>99180</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 25401-2026 artfynd.xlsx
+++ b/artfynd/A 25401-2026 artfynd.xlsx
@@ -675,53 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>134168910</v>
+        <v>134168911</v>
       </c>
       <c r="B2" t="n">
-        <v>99180</v>
+        <v>57972</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Vattentornet Bergsåker, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>615177</v>
+        <v>615173</v>
       </c>
       <c r="R2" t="n">
-        <v>6922983</v>
+        <v>6922963</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +755,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>11 st</t>
+          <t>Födosök</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,48 +787,53 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>134168911</v>
+        <v>134168910</v>
       </c>
       <c r="B3" t="n">
-        <v>57972</v>
+        <v>99180</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Vattentornet Bergsåker, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>615173</v>
+        <v>615177</v>
       </c>
       <c r="R3" t="n">
-        <v>6922963</v>
+        <v>6922983</v>
       </c>
       <c r="S3" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,12 +872,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Födosök</t>
+          <t>11 st</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 25401-2026 artfynd.xlsx
+++ b/artfynd/A 25401-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>134168910</v>
       </c>
       <c r="B2" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>134168909</v>
       </c>
       <c r="B4" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 25401-2026 artfynd.xlsx
+++ b/artfynd/A 25401-2026 artfynd.xlsx
@@ -675,53 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>134168910</v>
+        <v>134168911</v>
       </c>
       <c r="B2" t="n">
-        <v>99188</v>
+        <v>57972</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Vattentornet Bergsåker, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>615177</v>
+        <v>615173</v>
       </c>
       <c r="R2" t="n">
-        <v>6922983</v>
+        <v>6922963</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +755,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>11 st</t>
+          <t>Födosök</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,32 +787,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>134168911</v>
+        <v>134168909</v>
       </c>
       <c r="B3" t="n">
-        <v>57972</v>
+        <v>99195</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,13 +822,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>615173</v>
+        <v>615205</v>
       </c>
       <c r="R3" t="n">
-        <v>6922963</v>
+        <v>6922980</v>
       </c>
       <c r="S3" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,12 +867,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Födosök</t>
+          <t>9 plantor</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134168909</v>
+        <v>134168910</v>
       </c>
       <c r="B4" t="n">
-        <v>99188</v>
+        <v>99195</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -933,19 +928,24 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Vattentornet Bergsåker, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>615205</v>
+        <v>615177</v>
       </c>
       <c r="R4" t="n">
-        <v>6922980</v>
+        <v>6922983</v>
       </c>
       <c r="S4" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,12 +984,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>9 plantor</t>
+          <t>11 st</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 25401-2026 artfynd.xlsx
+++ b/artfynd/A 25401-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134168911</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -901,6 +911,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134168910</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1013,8 +1028,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134168909</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>